--- a/data/trans_orig/Q47-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su talla</t>
+          <t>Población según su talla (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>169,24; 170,05</t>
+          <t>169,19; 170,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>168,91; 169,87</t>
+          <t>168,96; 169,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168,66; 169,83</t>
+          <t>168,66; 169,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>157,95; 158,69</t>
+          <t>157,94; 158,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>158,18; 158,91</t>
+          <t>158,2; 158,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>158,37; 159,25</t>
+          <t>158,36; 159,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>158,32; 159,37</t>
+          <t>158,34; 159,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>162,92; 163,63</t>
+          <t>162,91; 163,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162,85; 163,66</t>
+          <t>162,89; 163,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163,39; 164,28</t>
+          <t>163,38; 164,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>162,64; 163,63</t>
+          <t>162,65; 163,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>174,22; 174,9</t>
+          <t>174,24; 174,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>173,79; 174,47</t>
+          <t>173,82; 174,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174,12; 174,78</t>
+          <t>174,1; 174,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174,02; 177,37</t>
+          <t>173,98; 177,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>161,88; 162,49</t>
+          <t>161,86; 162,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>161,7; 162,3</t>
+          <t>161,71; 162,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>161,88; 162,51</t>
+          <t>161,88; 162,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>159,63; 162,48</t>
+          <t>159,63; 162,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>168,25; 168,9</t>
+          <t>168,26; 168,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168,11; 168,7</t>
+          <t>168,12; 168,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168,12; 168,72</t>
+          <t>168,12; 168,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>166,61; 170,56</t>
+          <t>166,65; 170,53</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174,91; 176,11</t>
+          <t>174,88; 176,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175,64; 176,98</t>
+          <t>175,65; 176,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175,76; 177,05</t>
+          <t>175,68; 177,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175,36; 176,49</t>
+          <t>175,39; 176,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163,07; 164,24</t>
+          <t>163,05; 164,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>163,46; 164,74</t>
+          <t>163,48; 164,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162,6; 163,69</t>
+          <t>162,53; 163,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163,43; 164,26</t>
+          <t>163,41; 164,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>169,41; 170,53</t>
+          <t>169,43; 170,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169,72; 170,95</t>
+          <t>169,73; 170,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169,18; 170,31</t>
+          <t>169,19; 170,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169,34; 170,37</t>
+          <t>169,38; 170,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,42</t>
+          <t>172,92; 173,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,86; 173,39</t>
+          <t>172,84; 173,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173,57; 174,07</t>
+          <t>173,57; 174,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173,62; 176,13</t>
+          <t>173,63; 176,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,65; 161,11</t>
+          <t>160,69; 161,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,8; 161,28</t>
+          <t>160,8; 161,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,2; 161,68</t>
+          <t>161,18; 161,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>160,19; 162,04</t>
+          <t>160,25; 162,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,18</t>
+          <t>166,72; 167,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,77; 167,25</t>
+          <t>166,79; 167,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,29; 167,78</t>
+          <t>167,3; 167,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>166,82; 169,33</t>
+          <t>166,75; 169,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q47-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169,23</t>
+          <t>169,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>158,96</t>
+          <t>159,23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>163,23</t>
+          <t>163,57</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>169,19; 170,06</t>
+          <t>169,22; 170,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>168,96; 169,93</t>
+          <t>168,89; 169,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169,63; 170,72</t>
+          <t>169,69; 170,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168,66; 169,86</t>
+          <t>168,99; 170,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>157,94; 158,69</t>
+          <t>157,98; 158,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>158,2; 158,93</t>
+          <t>158,18; 158,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>158,36; 159,28</t>
+          <t>158,39; 159,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>158,34; 159,41</t>
+          <t>158,87; 159,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>162,91; 163,63</t>
+          <t>162,9; 163,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162,89; 163,64</t>
+          <t>162,81; 163,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163,38; 164,26</t>
+          <t>163,4; 164,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>162,65; 163,7</t>
+          <t>163,17; 164,06</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174,98</t>
+          <t>174,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>161,56</t>
+          <t>162,53</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>174,24; 174,9</t>
+          <t>174,2; 174,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>173,82; 174,48</t>
+          <t>173,79; 174,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174,1; 174,81</t>
+          <t>174,09; 174,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173,98; 177,22</t>
+          <t>173,77; 174,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>161,86; 162,48</t>
+          <t>161,89; 162,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>161,71; 162,29</t>
+          <t>161,7; 162,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>161,88; 162,47</t>
+          <t>161,87; 162,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>159,63; 162,53</t>
+          <t>162,31; 162,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>168,26; 168,88</t>
+          <t>168,23; 168,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168,12; 168,74</t>
+          <t>168,11; 168,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168,12; 168,73</t>
+          <t>168,16; 168,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>166,65; 170,53</t>
+          <t>168,12; 168,69</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175,89</t>
+          <t>175,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>163,86</t>
+          <t>163,82</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>169,84</t>
+          <t>169,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174,88; 176,14</t>
+          <t>174,91; 176,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175,65; 176,95</t>
+          <t>175,63; 176,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175,68; 177,03</t>
+          <t>175,76; 177,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175,39; 176,44</t>
+          <t>175,19; 176,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163,05; 164,2</t>
+          <t>162,99; 164,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>163,48; 164,78</t>
+          <t>163,45; 164,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162,53; 163,67</t>
+          <t>162,64; 163,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163,41; 164,29</t>
+          <t>163,43; 164,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>169,43; 170,6</t>
+          <t>169,4; 170,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169,73; 170,96</t>
+          <t>169,69; 170,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169,19; 170,4</t>
+          <t>169,21; 170,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169,38; 170,39</t>
+          <t>169,25; 170,14</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174,31</t>
+          <t>173,71</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>161,47</t>
+          <t>162,1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>167,79</t>
+          <t>167,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,44</t>
+          <t>172,91; 173,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,84; 173,4</t>
+          <t>172,86; 173,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173,57; 174,13</t>
+          <t>173,57; 174,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173,63; 176,07</t>
+          <t>173,44; 173,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,12</t>
+          <t>160,66; 161,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,8; 161,26</t>
+          <t>160,78; 161,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,18; 161,67</t>
+          <t>161,19; 161,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>160,25; 162,02</t>
+          <t>161,92; 162,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,19</t>
+          <t>166,73; 167,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,79; 167,25</t>
+          <t>166,77; 167,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,3; 167,77</t>
+          <t>167,32; 167,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>166,75; 169,24</t>
+          <t>167,55; 167,99</t>
         </is>
       </c>
     </row>
